--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Social Eagle AI Docs\Assignments\Assignment_W1_D3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C00968A-3188-4481-98BB-9C6DB4AD620A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EBDA3C-3874-4DDC-B32C-8F63E048AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Name</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>Rajesh Jio</t>
+  </si>
+  <si>
+    <t>9XXXXXXXXX</t>
+  </si>
+  <si>
+    <t>7XXXXXXXXX</t>
   </si>
 </sst>
 </file>
@@ -402,8 +408,8 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>9597182785</v>
+      <c r="B2" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -413,8 +419,8 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>7558105333</v>
+      <c r="B3" t="s">
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
